--- a/tools/importer/reports/import-credit-cards-hub.report.xlsx
+++ b/tools/importer/reports/import-credit-cards-hub.report.xlsx
@@ -52,7 +52,7 @@
     <t>credit-cards-hub</t>
   </si>
   <si>
-    <t>2026-04-09T22:31:01.962Z</t>
+    <t>2026-04-11T04:27:08.830Z</t>
   </si>
   <si>
     <t>Apply for a Credit Card Online | RBC Royal Bank of Canada</t>
